--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU 03/HRM/pre LAM_HRM-2031-0160/Panel-28/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU03_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU 03/HRM/pre LAM_HRM-2031-0160/Panel-28/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU03_Coupon_Front_Summary.xlsx
@@ -460,13 +460,13 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>17.15732</v>
+      </c>
+      <c r="D2" t="n">
+        <v>16.74663</v>
+      </c>
+      <c r="E2" t="n">
         <v>16.92765</v>
-      </c>
-      <c r="D2" t="n">
-        <v>17.15732</v>
-      </c>
-      <c r="E2" t="n">
-        <v>16.74663</v>
       </c>
       <c r="F2" t="n">
         <v>42.47657</v>
@@ -567,13 +567,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.49947</v>
+        <v>16.5408</v>
       </c>
       <c r="D6" t="n">
         <v>16.28155</v>
       </c>
       <c r="E6" t="n">
-        <v>16.5408</v>
+        <v>16.49947</v>
       </c>
       <c r="F6" t="n">
         <v>22.04434</v>
@@ -611,13 +611,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.44818</v>
+        <v>16.53172</v>
       </c>
       <c r="D8" t="n">
         <v>16.06349</v>
       </c>
       <c r="E8" t="n">
-        <v>16.53172</v>
+        <v>16.44818</v>
       </c>
       <c r="F8" t="n">
         <v>21.9976</v>
